--- a/artfynd/A 39520-2026 artfynd.xlsx
+++ b/artfynd/A 39520-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137461625</v>
       </c>
       <c r="B2" t="n">
-        <v>96646</v>
+        <v>96650</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137462884</v>
       </c>
       <c r="B3" t="n">
-        <v>92399</v>
+        <v>92403</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137464456</v>
       </c>
       <c r="B4" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137463454</v>
       </c>
       <c r="B5" t="n">
-        <v>99412</v>
+        <v>99416</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137461406</v>
       </c>
       <c r="B6" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
